--- a/base_dados_pedro_morgado.xlsx
+++ b/base_dados_pedro_morgado.xlsx
@@ -549,7 +549,7 @@
         <v>Sim</v>
       </c>
       <c r="P2" t="str">
-        <v>2026-07-16T14:37:44.185Z</v>
+        <v>2026-07-17T15:48:25.957Z</v>
       </c>
       <c r="Q2" t="str">
         <v/>
@@ -602,7 +602,7 @@
         <v>Sim</v>
       </c>
       <c r="P3" t="str">
-        <v>2026-07-16T14:37:44.185Z</v>
+        <v>2026-07-17T15:48:25.957Z</v>
       </c>
       <c r="Q3" t="str">
         <v/>

--- a/base_dados_pedro_morgado.xlsx
+++ b/base_dados_pedro_morgado.xlsx
@@ -549,7 +549,7 @@
         <v>Sim</v>
       </c>
       <c r="P2" t="str">
-        <v>2026-07-17T15:48:25.957Z</v>
+        <v>2026-07-17T16:43:35.893Z</v>
       </c>
       <c r="Q2" t="str">
         <v/>
@@ -602,7 +602,7 @@
         <v>Sim</v>
       </c>
       <c r="P3" t="str">
-        <v>2026-07-17T15:48:25.957Z</v>
+        <v>2026-07-17T16:43:35.893Z</v>
       </c>
       <c r="Q3" t="str">
         <v/>

--- a/base_dados_pedro_morgado.xlsx
+++ b/base_dados_pedro_morgado.xlsx
@@ -549,7 +549,7 @@
         <v>Sim</v>
       </c>
       <c r="P2" t="str">
-        <v>2026-07-17T16:43:35.893Z</v>
+        <v>2026-07-20T13:14:08.639Z</v>
       </c>
       <c r="Q2" t="str">
         <v/>
@@ -602,7 +602,7 @@
         <v>Sim</v>
       </c>
       <c r="P3" t="str">
-        <v>2026-07-17T16:43:35.893Z</v>
+        <v>2026-07-20T13:14:08.639Z</v>
       </c>
       <c r="Q3" t="str">
         <v/>
